--- a/Data_sorted.xlsx
+++ b/Data_sorted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evancaenegem\Documents\Doctorat\8.Mémoires master\Marche\Data_Analyse_Walk_R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evancaenegem\Documents\Doctorat\3.Recherches et projets en cours\WP4_Walking timing paper\Data_Analyse_Walk_R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33143DF2-CBB9-4DEE-A1D2-E73BFD1EF53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{559FC8CD-1BBE-42BF-B0E6-7A6546AA7B89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="100" windowWidth="19380" windowHeight="11180" xr2:uid="{39358E39-EE7A-411E-9669-876B819D7DEF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{39358E39-EE7A-411E-9669-876B819D7DEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Données Brutes" sheetId="1" r:id="rId1"/>
@@ -711,6 +711,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -718,7 +719,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1190,6 +1190,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1197,7 +1198,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1672,6 +1672,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1679,7 +1680,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2702,6 +2702,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2709,7 +2710,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="P8">
         <f>AVERAGE(D2:D31)</f>
-        <v>60.866666666666667</v>
+        <v>60.233333333333334</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="P9">
         <f>STDEV(D2:D31)</f>
-        <v>7.9729427498229155</v>
+        <v>8.5123979900043416</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -6049,7 +6049,7 @@
         <v>22</v>
       </c>
       <c r="D14">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E14">
         <v>4.1900000000000004</v>
@@ -6151,7 +6151,7 @@
         <v>21</v>
       </c>
       <c r="D16">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16">
         <v>3.59</v>
@@ -6239,7 +6239,7 @@
         <v>20</v>
       </c>
       <c r="D18">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E18">
         <v>3.73</v>
@@ -6418,7 +6418,7 @@
         <v>22</v>
       </c>
       <c r="D22">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E22">
         <v>3.73</v>
@@ -6462,7 +6462,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E23">
         <v>3.92</v>
@@ -6594,7 +6594,7 @@
         <v>23</v>
       </c>
       <c r="D26">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E26">
         <v>3.66</v>
